--- a/Files-Bernd/Data/2025-08-27-Dataset.xlsx
+++ b/Files-Bernd/Data/2025-08-27-Dataset.xlsx
@@ -61147,13 +61147,10 @@
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <Status xmlns="4266979c-f9d5-480d-8e7f-fd5babe08436" xsi:nil="true"/>
-    <TaxCatchAll xmlns="8fe787a5-7476-4b36-a333-c20c98769fb2" xsi:nil="true"/>
-    <Thumbnail xmlns="4266979c-f9d5-480d-8e7f-fd5babe08436" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4266979c-f9d5-480d-8e7f-fd5babe08436">
+    <TaxCatchAll xmlns="50882fb6-7b37-4016-bc4e-645c0637b088" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bd451b29-8fb7-40f7-9106-962108d7f4ae">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
-    <Meetingdate xmlns="4266979c-f9d5-480d-8e7f-fd5babe08436" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
@@ -61168,37 +61165,32 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008AAEEF9F6F9A384ABAE8D2ECECBBC7B3" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fcf0f72b08134e7b4245ffaa94ec38a3">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0689230e-2366-4480-b5f6-6c63b13f0f35" xmlns:ns3="4266979c-f9d5-480d-8e7f-fd5babe08436" xmlns:ns4="8fe787a5-7476-4b36-a333-c20c98769fb2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="abb9debeedb6778b787a7aad2b7fc6f7" ns2:_="" ns3:_="" ns4:_="">
-    <xsd:import namespace="0689230e-2366-4480-b5f6-6c63b13f0f35"/>
-    <xsd:import namespace="4266979c-f9d5-480d-8e7f-fd5babe08436"/>
-    <xsd:import namespace="8fe787a5-7476-4b36-a333-c20c98769fb2"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FEC3B82CDE999F468FCF6EE52EBE2A67" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="40b19084bb4a9c78ae6ece17757b47f9">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bd451b29-8fb7-40f7-9106-962108d7f4ae" xmlns:ns3="35149867-cd7a-4969-a555-76a8777aa585" xmlns:ns4="50882fb6-7b37-4016-bc4e-645c0637b088" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="82b6cdac0984816eaf9ebfdf6799bd5e" ns2:_="" ns3:_="" ns4:_="">
+    <xsd:import namespace="bd451b29-8fb7-40f7-9106-962108d7f4ae"/>
+    <xsd:import namespace="35149867-cd7a-4969-a555-76a8777aa585"/>
+    <xsd:import namespace="50882fb6-7b37-4016-bc4e-645c0637b088"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:Status" minOccurs="0"/>
-                <xsd:element ref="ns3:Thumbnail" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns3:Meetingdate" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -61206,10 +61198,80 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0689230e-2366-4480-b5f6-6c63b13f0f35" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="bd451b29-8fb7-40f7-9106-962108d7f4ae" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="15" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="8c631306-648b-4820-82d0-96e941587191" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="19" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="20" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="21" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="22" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="23" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="35149867-cd7a-4969-a555-76a8777aa585" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -61228,7 +61290,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -61236,111 +61298,10 @@
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="4266979c-f9d5-480d-8e7f-fd5babe08436" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="50882fb6-7b37-4016-bc4e-645c0637b088" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="19" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="20" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c3ea2160-29c6-45a3-9bc6-8bc28cb0899c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Status" ma:index="25" nillable="true" ma:displayName="Status" ma:format="Dropdown" ma:internalName="Status">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Choice">
-          <xsd:enumeration value="Drafted"/>
-          <xsd:enumeration value="Checked"/>
-          <xsd:enumeration value="Approved"/>
-          <xsd:enumeration value="Final"/>
-          <xsd:enumeration value="Return for Edits"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Thumbnail" ma:index="26" nillable="true" ma:displayName="Thumbnail" ma:format="Thumbnail" ma:internalName="Thumbnail">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="27" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Meetingdate" ma:index="28" nillable="true" ma:displayName="Meeting date" ma:format="DateOnly" ma:internalName="Meetingdate">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8fe787a5-7476-4b36-a333-c20c98769fb2" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{8bc653ce-d70c-4fc1-b0ba-7258336a0037}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="0689230e-2366-4480-b5f6-6c63b13f0f35">
+    <xsd:element name="TaxCatchAll" ma:index="16" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{2ffea220-ab26-4efa-aaa9-07be208f4560}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="35149867-cd7a-4969-a555-76a8777aa585">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:MultiChoiceLookup">
@@ -61460,5 +61421,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A035ABD1-0C84-4E25-A013-BBD23F6280F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF1F2305-00FC-48DD-AC38-0F5D66817504}"/>
 </file>